--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,48 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130894768</v>
+        <v>130894783</v>
       </c>
       <c r="B5" t="n">
-        <v>91739</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöändan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407178</v>
+        <v>407191</v>
       </c>
       <c r="R5" t="n">
-        <v>7011146</v>
+        <v>7011101</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,31 +1066,35 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1112,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130894783</v>
+        <v>130894776</v>
       </c>
       <c r="B6" t="n">
         <v>57864</v>
@@ -1147,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407191</v>
+        <v>406805</v>
       </c>
       <c r="R6" t="n">
-        <v>7011101</v>
+        <v>7010911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1224,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130894776</v>
+        <v>130894778</v>
       </c>
       <c r="B7" t="n">
         <v>57864</v>
@@ -1259,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406805</v>
+        <v>406741</v>
       </c>
       <c r="R7" t="n">
-        <v>7010911</v>
+        <v>7010874</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1336,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130894778</v>
+        <v>130894777</v>
       </c>
       <c r="B8" t="n">
         <v>57864</v>
@@ -1371,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406741</v>
+        <v>406773</v>
       </c>
       <c r="R8" t="n">
-        <v>7010874</v>
+        <v>7010852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1448,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130894777</v>
+        <v>130894770</v>
       </c>
       <c r="B9" t="n">
         <v>57864</v>
@@ -1483,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406773</v>
+        <v>407137</v>
       </c>
       <c r="R9" t="n">
-        <v>7010852</v>
+        <v>7011111</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,22 +1514,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1560,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130894765</v>
+        <v>130894760</v>
       </c>
       <c r="B10" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,33 +1572,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöändan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407113</v>
+        <v>406786</v>
       </c>
       <c r="R10" t="n">
-        <v>7011090</v>
+        <v>7010890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,36 +1626,30 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Högstubbe av gran</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1672,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130894759</v>
+        <v>130894767</v>
       </c>
       <c r="B11" t="n">
-        <v>57861</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,16 +1679,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1701,20 +1697,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sjöändan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406786</v>
+        <v>407194</v>
       </c>
       <c r="R11" t="n">
-        <v>7010890</v>
+        <v>7011100</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,29 +1733,34 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1783,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130894770</v>
+        <v>130894782</v>
       </c>
       <c r="B12" t="n">
         <v>57864</v>
@@ -1818,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407137</v>
+        <v>407192</v>
       </c>
       <c r="R12" t="n">
-        <v>7011111</v>
+        <v>7011093</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,22 +1845,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1895,7 +1892,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130894767</v>
+        <v>130894766</v>
       </c>
       <c r="B13" t="n">
         <v>57864</v>
@@ -1933,7 +1930,7 @@
         <v>407194</v>
       </c>
       <c r="R13" t="n">
-        <v>7011100</v>
+        <v>7011099</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,7 +1972,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2007,7 +2004,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130894760</v>
+        <v>130894780</v>
       </c>
       <c r="B14" t="n">
         <v>79221</v>
@@ -2042,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406786</v>
+        <v>406817</v>
       </c>
       <c r="R14" t="n">
-        <v>7010890</v>
+        <v>7010950</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,22 +2069,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,10 +2111,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130894757</v>
+        <v>130894769</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>91796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,37 +2122,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sjöändan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406761</v>
+        <v>407179</v>
       </c>
       <c r="R15" t="n">
-        <v>7010920</v>
+        <v>7011114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2182,31 +2172,30 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2222,440 +2211,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>130894782</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57864</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Sjöändan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>407192</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7011093</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-01-24</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-01-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>130894766</v>
-      </c>
-      <c r="B17" t="n">
-        <v>57864</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Sjöändan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>407194</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7011099</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>130894780</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79221</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Sjöändan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>406817</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7010950</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-01-24</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-01-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>130894769</v>
-      </c>
-      <c r="B19" t="n">
-        <v>91796</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Sjöändan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>407179</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7011114</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -2114,7 +2114,7 @@
         <v>130894769</v>
       </c>
       <c r="B15" t="n">
-        <v>91796</v>
+        <v>91804</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130894781</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130894756</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130894761</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130894783</v>
       </c>
       <c r="B5" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130894776</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130894778</v>
       </c>
       <c r="B7" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>130894777</v>
       </c>
       <c r="B8" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>130894770</v>
       </c>
       <c r="B9" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>130894760</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>130894767</v>
       </c>
       <c r="B11" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>130894782</v>
       </c>
       <c r="B12" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>130894766</v>
       </c>
       <c r="B13" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>130894780</v>
       </c>
       <c r="B14" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>130894769</v>
       </c>
       <c r="B15" t="n">
-        <v>91804</v>
+        <v>91818</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130894760</v>
+        <v>130894767</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406786</v>
+        <v>407194</v>
       </c>
       <c r="R10" t="n">
-        <v>7010890</v>
+        <v>7011100</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,22 +1626,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130894767</v>
+        <v>130894760</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407194</v>
+        <v>406786</v>
       </c>
       <c r="R11" t="n">
-        <v>7011100</v>
+        <v>7010890</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,27 +1738,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130894767</v>
+        <v>130894760</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407194</v>
+        <v>406786</v>
       </c>
       <c r="R10" t="n">
-        <v>7011100</v>
+        <v>7010890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,27 +1626,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130894760</v>
+        <v>130894767</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406786</v>
+        <v>407194</v>
       </c>
       <c r="R11" t="n">
-        <v>7010890</v>
+        <v>7011100</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,22 +1733,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130894756</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130894761</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130894760</v>
+        <v>130894767</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406786</v>
+        <v>407194</v>
       </c>
       <c r="R10" t="n">
-        <v>7010890</v>
+        <v>7011100</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,22 +1626,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130894767</v>
+        <v>130894760</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407194</v>
+        <v>406786</v>
       </c>
       <c r="R11" t="n">
-        <v>7011100</v>
+        <v>7010890</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,27 +1738,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130894782</v>
+        <v>130894766</v>
       </c>
       <c r="B12" t="n">
         <v>57884</v>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407192</v>
+        <v>407194</v>
       </c>
       <c r="R12" t="n">
-        <v>7011093</v>
+        <v>7011099</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,22 +1845,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1892,7 +1892,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130894766</v>
+        <v>130894782</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407194</v>
+        <v>407192</v>
       </c>
       <c r="R13" t="n">
-        <v>7011099</v>
+        <v>7011093</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,22 +1957,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2007,7 +2007,7 @@
         <v>130894780</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>130894769</v>
       </c>
       <c r="B15" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -2217,7 +2217,7 @@
         <v>131200971</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>131200961</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57990</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -2217,7 +2217,7 @@
         <v>131200971</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>131200961</v>
       </c>
       <c r="B17" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -2217,7 +2217,7 @@
         <v>131200971</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>131200961</v>
       </c>
       <c r="B17" t="n">
-        <v>57991</v>
+        <v>57992</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -2217,7 +2217,7 @@
         <v>131200971</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>131200961</v>
       </c>
       <c r="B17" t="n">
-        <v>57992</v>
+        <v>57995</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -2217,7 +2217,7 @@
         <v>131200971</v>
       </c>
       <c r="B16" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>131200961</v>
       </c>
       <c r="B17" t="n">
-        <v>57995</v>
+        <v>57996</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130894781</v>
+        <v>130894756</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407119</v>
+        <v>406770</v>
       </c>
       <c r="R2" t="n">
-        <v>7011110</v>
+        <v>7010906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130894756</v>
+        <v>130894760</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406770</v>
+        <v>406786</v>
       </c>
       <c r="R3" t="n">
-        <v>7010906</v>
+        <v>7010890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,11 +892,11 @@
         <v>130894761</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1001,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130894783</v>
+        <v>130894780</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407191</v>
+        <v>406817</v>
       </c>
       <c r="R5" t="n">
-        <v>7011101</v>
+        <v>7010950</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130894776</v>
+        <v>130894766</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406805</v>
+        <v>407194</v>
       </c>
       <c r="R6" t="n">
-        <v>7010911</v>
+        <v>7011099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1225,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130894778</v>
+        <v>130894767</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406741</v>
+        <v>407194</v>
       </c>
       <c r="R7" t="n">
-        <v>7010874</v>
+        <v>7011100</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,22 +1280,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1337,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130894777</v>
+        <v>130894770</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406773</v>
+        <v>407137</v>
       </c>
       <c r="R8" t="n">
-        <v>7010852</v>
+        <v>7011111</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,22 +1392,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1449,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130894770</v>
+        <v>130894771</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1477,7 @@
         <v>407137</v>
       </c>
       <c r="R9" t="n">
-        <v>7011111</v>
+        <v>7011044</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1561,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130894767</v>
+        <v>130894773</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407194</v>
+        <v>406878</v>
       </c>
       <c r="R10" t="n">
-        <v>7011100</v>
+        <v>7010791</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1673,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130894760</v>
+        <v>130894776</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406786</v>
+        <v>406805</v>
       </c>
       <c r="R11" t="n">
-        <v>7010890</v>
+        <v>7010911</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,22 +1728,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130894766</v>
+        <v>130894777</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407194</v>
+        <v>406773</v>
       </c>
       <c r="R12" t="n">
-        <v>7011099</v>
+        <v>7010852</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,22 +1840,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1892,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130894782</v>
+        <v>130894778</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407192</v>
+        <v>406741</v>
       </c>
       <c r="R13" t="n">
-        <v>7011093</v>
+        <v>7010874</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1972,7 +1967,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2004,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130894780</v>
+        <v>130894781</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,21 +2010,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406817</v>
+        <v>407119</v>
       </c>
       <c r="R14" t="n">
-        <v>7010950</v>
+        <v>7011110</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,7 +2069,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2079,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,10 +2111,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130894769</v>
+        <v>130894782</v>
       </c>
       <c r="B15" t="n">
-        <v>91830</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,19 +2122,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2142,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407179</v>
+        <v>407192</v>
       </c>
       <c r="R15" t="n">
-        <v>7011114</v>
+        <v>7011093</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,22 +2176,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2214,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131200971</v>
+        <v>130894783</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2243,24 +2252,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sjöändan, Lakanäset, Undersåker, Jmt</t>
+          <t>Sjöändan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407157</v>
+        <v>407191</v>
       </c>
       <c r="R16" t="n">
-        <v>7011090</v>
+        <v>7011101</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,27 +2288,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,39 +2323,39 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Filip Aguirre</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Filip Aguirre</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131200961</v>
+        <v>131200971</v>
       </c>
       <c r="B17" t="n">
-        <v>58002</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2362,14 +2363,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2425,6 +2426,11 @@
           <t>11:20</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2446,6 +2452,121 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131200961</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sjöändan, Lakanäset, Undersåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>407157</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7011090</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Filip Aguirre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Filip Aguirre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62621-2025 artfynd.xlsx
+++ b/artfynd/A 62621-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894756</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894760</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894761</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894780</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894766</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894767</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894770</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894771</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894773</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894776</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1884,6 +1939,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894777</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1996,6 +2056,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894778</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2108,6 +2173,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894781</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2220,6 +2290,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894782</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2332,6 +2407,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894783</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2452,6 +2532,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131200971</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2567,8 +2652,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131200961</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>